--- a/data/kz/05_tax_regimes.xlsx
+++ b/data/kz/05_tax_regimes.xlsx
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ASTANA</t>
+          <t>astana</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ALMATY</t>
+          <t>almaty</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SHYMKENT</t>
+          <t>shymkent</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AKTOBE</t>
+          <t>aktobe</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KARAGANDA</t>
+          <t>karaganda</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ATYRAU</t>
+          <t>atyrau</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AKTAU</t>
+          <t>aktau</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KOSTANAY</t>
+          <t>kostanay</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PAVLODAR</t>
+          <t>pavlodar</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SEMEY</t>
+          <t>semey</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>USKAMAN</t>
+          <t>oskemen</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TARAZ</t>
+          <t>taraz</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TURKESTAN</t>
+          <t>turkestan</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PETROPAVL</t>
+          <t>petropavl</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KOKSHETAU</t>
+          <t>kokshetau</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -2221,19 +2221,14 @@
           <t>ВАЖНО: Данные актуальны на март 2026</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Ключевые изменения НК РК 2026 vs 2025:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2241,7 +2236,6 @@
           <t>1. МРП: 3 932 → 4 325 ₸ (+10%)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2249,7 +2243,6 @@
           <t>2. НДС: 12% → 16%</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2257,7 +2250,6 @@
           <t>3. УД ставка: 3% → 4% базовая (маслихаты 2-6%)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2265,7 +2257,6 @@
           <t>4. ОПВР: 2.5% → 3.5%</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2273,7 +2264,6 @@
           <t>5. Лимит УД: 180 млн → 600 000 МРП (~2.6 млрд)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2281,7 +2271,6 @@
           <t>6. Лимит сотрудников УД: 30 → без ограничений</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2289,7 +2278,6 @@
           <t>7. Соцналог для УД: ОТМЕНЁН</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2297,7 +2285,6 @@
           <t>8. УД + розничный налог: ОБЪЕДИНЕНЫ в единый режим</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2305,7 +2292,6 @@
           <t>9. ИПН: плоская 10% → прогрессивная 10/15%</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2313,19 +2299,14 @@
           <t>10. Дивиденды ИПН: 10% → 5% (до 230 000 МРП)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>B2B нюанс:</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2333,7 +2314,6 @@
           <t>ЮЛ на ОУР НЕ могут взять в вычет/зачёт расходы</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2341,7 +2321,6 @@
           <t>по сделкам с контрагентами на УД (упрощёнке).</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2349,7 +2328,6 @@
           <t>Для B2B ниш (корп. клининг и т.д.) это критично —</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2357,19 +2335,14 @@
           <t>клиенты могут предпочесть поставщика на ОУР.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>Ставки по городам:</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2377,7 +2350,6 @@
           <t>Большинство маслихатов снизили ставку до 2-3%.</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2385,7 +2357,6 @@
           <t>6% НЕ применяется ни в одном регионе.</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2393,7 +2364,6 @@
           <t>Проверять ежегодно — маслихаты принимают решения до 1 декабря.</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kz/05_tax_regimes.xlsx
+++ b/data/kz/05_tax_regimes.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tax_regimes_2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="city_ud_rates_2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b2b_nds_warnings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payroll_taxes_2026" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="key_params_2026" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b2b_nds_warnings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payroll_taxes_2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="key_params_2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,572 +749,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>city_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>city_name_ru</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>region_ru</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ud_rate_pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>maslikhat_decision</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>decision_date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>notes_ru</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>astana</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Астана</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>г. Астана</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Решение №349/46-VIII</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>28.11.2025</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>mybuh.kz</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Рабочая группа изучает снижение до 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>almaty</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Алматы</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>г. Алматы</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Решение №256</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>28.11.2025</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>uchet.kz</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>shymkent</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Шымкент</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>г. Шымкент</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Решение маслихата</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>ноябрь 2025</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>bes.media</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Самая низкая среди мегаполисов</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>aktobe</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Актобе</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Актюбинская обл.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Решение №356</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18.11.2025</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>uchet.kz</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10 районов области — 2%, Актобе и 2 района — 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>karaganda</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Караганда</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Карагандинская обл.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Уточнить решение маслихата</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>atyrau</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Атырау</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Атырауская обл.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>aktau</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Актау</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Мангистауская обл.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>kostanay</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Костанай</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Костанайская обл.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Решение маслихата</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>ноябрь 2025</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>pro1c.kz</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Вся область — 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>pavlodar</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Павлодар</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Павлодарская обл.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Решение маслихата</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>ноябрь 2025</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>pro1c.kz</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Вся область — 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>semey</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Семей</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Абайская обл.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>oskemen</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Усть-Каменогорск</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>ВКО</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>taraz</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Тараз</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Жамбылская обл.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>turkestan</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Туркестан</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Туркестанская обл.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Уточнить — предположительно 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>petropavl</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Петропавловск</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>СКО</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Решение маслихата</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>ноябрь 2025</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>pro1c.kz</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Вся СКО — 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>kokshetau</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Кокшетау</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Акмолинская обл.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Часть районов — 2%, город уточнить</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1601,7 +1034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1857,7 +1290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2203,13 +1636,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -2222,7 +1655,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2300,7 +1732,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -2336,7 +1767,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
